--- a/modules/tracker/docs/templates/Tracking_Config.xlsx
+++ b/modules/tracker/docs/templates/Tracking_Config.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
   <si>
     <t xml:space="preserve">TURAS Tracker - Configuration Settings</t>
   </si>
@@ -89,6 +89,15 @@
     <t xml:space="preserve">Relative or absolute directory path</t>
   </si>
   <si>
+    <t xml:space="preserve">question_mapping_file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Path to question mapping file (auto-detected if blank)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filename, relative path, or absolute path (e.g., Question_Mapping.xlsx)</t>
+  </si>
+  <si>
     <t xml:space="preserve">REPORTS</t>
   </si>
   <si>
@@ -101,7 +110,7 @@
     <t xml:space="preserve">Comma-separated list of report types to generate</t>
   </si>
   <si>
-    <t xml:space="preserve">detailed, wave_history, dashboard, sig_matrix</t>
+    <t xml:space="preserve">detailed, wave_history, dashboard, sig_matrix, tracking_crosstab</t>
   </si>
   <si>
     <t xml:space="preserve">html_report</t>
@@ -1221,80 +1230,80 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="s">
+      <c r="A10" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
+      <c r="B10" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="13" t="s">
+      <c r="A11" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="14" t="s">
-        <v>28</v>
-      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
     </row>
     <row r="12">
       <c r="A12" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>30</v>
       </c>
       <c r="C12" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="14" t="s">
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="s">
+      <c r="B13" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
+      <c r="C13" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="E14" s="14" t="s">
+      <c r="A14" s="9" t="s">
         <v>36</v>
       </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
     </row>
     <row r="15">
       <c r="A15" s="15" t="s">
         <v>37</v>
       </c>
       <c r="B15" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" s="16" t="s">
         <v>4</v>
@@ -1303,32 +1312,32 @@
         <v>38</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B16" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="11" t="s">
         <v>42</v>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>4</v>
@@ -1337,58 +1346,58 @@
         <v>43</v>
       </c>
       <c r="E17" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="s">
+      <c r="B18" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
+      <c r="C18" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" s="11" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" s="14" t="s">
+      <c r="A19" s="9" t="s">
         <v>48</v>
       </c>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
     </row>
     <row r="20">
       <c r="A20" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="11" t="s">
-        <v>50</v>
+      <c r="B20" s="11" t="n">
+        <v>0.05</v>
       </c>
       <c r="C20" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D20" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="14" t="s">
         <v>51</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>53</v>
-      </c>
-      <c r="B21" s="11" t="n">
-        <v>30</v>
       </c>
       <c r="C21" s="16" t="s">
         <v>4</v>
@@ -1404,17 +1413,17 @@
       <c r="A22" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>57</v>
+      <c r="B22" s="11" t="n">
+        <v>30</v>
       </c>
       <c r="C22" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D22" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E22" s="14" t="s">
         <v>58</v>
-      </c>
-      <c r="E22" s="14" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="23">
@@ -1422,93 +1431,93 @@
         <v>59</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="C23" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
+      <c r="B24" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="B25" s="11" t="s">
+      <c r="A25" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C26" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E25" s="14" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
+      <c r="D26" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D27" s="13" t="s">
+      <c r="A27" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E27" s="14" t="s">
-        <v>70</v>
-      </c>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28" s="11" t="s">
         <v>71</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>72</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D28" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="E28" s="14" t="s">
         <v>73</v>
-      </c>
-      <c r="E28" s="14" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>75</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>14</v>
       </c>
       <c r="C29" s="16" t="s">
         <v>4</v>
@@ -1534,12 +1543,12 @@
         <v>79</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>14</v>
@@ -1548,10 +1557,10 @@
         <v>4</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32">
@@ -1568,12 +1577,12 @@
         <v>84</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B33" s="11" t="s">
         <v>14</v>
@@ -1582,10 +1591,10 @@
         <v>4</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34">
@@ -1606,30 +1615,30 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
+      <c r="B35" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="E36" s="14" t="s">
+      <c r="A36" s="9" t="s">
         <v>94</v>
       </c>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
     </row>
     <row r="37">
       <c r="A37" s="15" t="s">
@@ -1645,7 +1654,24 @@
         <v>96</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>77</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1653,18 +1679,14 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A36:E36"/>
   </mergeCells>
   <dataValidations count="5">
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B14:B14">
-      <formula1>0</formula1>
-      <formula2>3</formula2>
-    </dataValidation>
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B15:B15">
       <formula1>0</formula1>
       <formula2>3</formula2>
@@ -1673,11 +1695,15 @@
       <formula1>0</formula1>
       <formula2>3</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B19:B19">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B17:B17">
+      <formula1>0</formula1>
+      <formula2>3</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20:B20">
       <formula1>0.01</formula1>
       <formula2>0.1</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B21:B21">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B22:B22">
       <formula1>10</formula1>
       <formula2>500</formula2>
     </dataValidation>
@@ -1689,33 +1715,33 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>"detailed,wave_history,dashboard,sig_matrix,detailed,wave_history,detailed,dashboard,detailed,wave_history,dashboard,sig_matrix"</xm:f>
+            <xm:f>"detailed,wave_history,dashboard,sig_matrix,tracking_crosstab,detailed,wave_history,detailed,dashboard,detailed,wave_history,dashboard,sig_matrix,detailed,wave_history,dashboard,sig_matrix,tracking_crosstab"</xm:f>
           </x14:formula1>
-          <xm:sqref>B11:B11</xm:sqref>
+          <xm:sqref>B12:B12</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"Y,N"</xm:f>
           </x14:formula1>
-          <xm:sqref>B12:B12</xm:sqref>
+          <xm:sqref>B13:B13</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>".,,"</xm:f>
           </x14:formula1>
-          <xm:sqref>B17:B17</xm:sqref>
+          <xm:sqref>B18:B18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"0.90,0.95,0.99"</xm:f>
           </x14:formula1>
-          <xm:sqref>B20:B20</xm:sqref>
+          <xm:sqref>B21:B21</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"Y,N"</xm:f>
           </x14:formula1>
-          <xm:sqref>B22:B22</xm:sqref>
+          <xm:sqref>B23:B23</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1740,84 +1766,84 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G5" s="17" t="s">
         <v>14</v>
@@ -1828,22 +1854,22 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C6" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F6" s="17" t="s">
         <v>123</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>120</v>
       </c>
       <c r="G6" s="17" t="s">
         <v>14</v>
@@ -1854,22 +1880,22 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G7" s="17" t="s">
         <v>14</v>
@@ -2104,173 +2130,173 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F6" s="17" t="n">
         <v>2</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F7" s="17" t="n">
         <v>3</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="F8" s="17" t="n">
         <v>4</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F9" s="17" t="n">
         <v>5</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10">
@@ -2765,97 +2791,97 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8">

--- a/modules/tracker/docs/templates/Tracking_Config.xlsx
+++ b/modules/tracker/docs/templates/Tracking_Config.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="269">
   <si>
     <t xml:space="preserve">TURAS Tracker - Configuration Settings</t>
   </si>
@@ -125,6 +125,15 @@
     <t xml:space="preserve">Y or N</t>
   </si>
   <si>
+    <t xml:space="preserve">dashboard_hero_metrics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comma-separated QuestionCodes to highlight as hero metrics on the HTML dashboard summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuestionCodes from TrackedQuestions (e.g., Q01_NPS,Q02_CSAT)</t>
+  </si>
+  <si>
     <t xml:space="preserve">FORMATTING</t>
   </si>
   <si>
@@ -212,6 +221,12 @@
     <t xml:space="preserve">A WaveID from the Waves sheet (e.g., W1)</t>
   </si>
   <si>
+    <t xml:space="preserve">show_sample_sizes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Display sample sizes (n=) in report output</t>
+  </si>
+  <si>
     <t xml:space="preserve">WEIGHTING</t>
   </si>
   <si>
@@ -299,6 +314,156 @@
     <t xml:space="preserve">Phone number</t>
   </si>
   <si>
+    <t xml:space="preserve">DEFAULT TRACKING SPECS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">default_rating_specs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Default TrackingSpecs for Rating/Likert questions (used when TrackingSpecs is blank)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comma-separated: mean, top_box, top2_box, top3_box, bottom_box, bottom2_box, distribution, range:X-Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">default_nps_specs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Default TrackingSpecs for NPS questions (used when TrackingSpecs is blank)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comma-separated: nps_score, promoters_pct, passives_pct, detractors_pct, full</t>
+  </si>
+  <si>
+    <t xml:space="preserve">default_single_response_specs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Default TrackingSpecs for Single_Response questions (used when TrackingSpecs is blank)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comma-separated: all, top3, category:X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">default_multi_mention_specs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Default TrackingSpecs for Multi_Mention questions (used when TrackingSpecs is blank)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comma-separated: auto, any, count_mean, count_distribution, option:X, category:X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">default_composite_specs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Default TrackingSpecs for Composite/Index questions (used when TrackingSpecs is blank)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comma-separated: mean, top_box, top2_box, top3_box, distribution, range:X-Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEATMAP THRESHOLDS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heatmap_pct_green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentage threshold for green (good) heatmap colouring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numeric 0-100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heatmap_pct_amber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentage threshold for amber (caution) heatmap colouring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heatmap_mean5_green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean score (5-point scale) threshold for green heatmap colouring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numeric 1.0-5.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heatmap_mean5_amber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean score (5-point scale) threshold for amber heatmap colouring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heatmap_mean10_green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean score (10-point scale) threshold for green heatmap colouring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numeric 1.0-10.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heatmap_mean10_amber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean score (10-point scale) threshold for amber heatmap colouring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heatmap_nps_green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPS threshold for green heatmap colouring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integer -100 to 100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heatmap_nps_amber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPS threshold for amber heatmap colouring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heatmap_response_green</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response percentage threshold for green heatmap colouring (pct_response metrics)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heatmap_response_amber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Response percentage threshold for amber heatmap colouring (pct_response metrics)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHARTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">segment_palette_preset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">default</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colour palette preset for banner segment charts in HTML reports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">default, muted, vibrant, or monochrome</t>
+  </si>
+  <si>
     <t xml:space="preserve">OTHER</t>
   </si>
   <si>
@@ -317,6 +482,15 @@
     <t xml:space="preserve">Notes to include in report appendix or footer</t>
   </si>
   <si>
+    <t xml:space="preserve">annotations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-configured chart annotations as JSON array (e.g., [{"metricId":"Q01","waveId":"W2","text":"Campaign launched"}])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JSON array string or leave blank</t>
+  </si>
+  <si>
     <t xml:space="preserve">TURAS Tracker - Wave Definitions</t>
   </si>
   <si>
@@ -464,7 +638,7 @@
     <t xml:space="preserve">[Optional] Display order within the report (1 = first)</t>
   </si>
   <si>
-    <t xml:space="preserve">[Optional] Comma-separated metrics to calculate: mean, top_box, top2_box, top3_box, bottom_box, bottom2_box, distribution, nps_score, promoters_pct, passives_pct, detractors_pct, full, all, auto, count_mean, range:X-Y, category:X, option:X</t>
+    <t xml:space="preserve">[Optional] Comma-separated metrics to calculate: mean, top_box, top2_box, top3_box, bottom_box, bottom2_box, bottom3_box, distribution, nps_score, promoters_pct, passives_pct, detractors_pct, full, all, auto, count_mean, count_distribution, range:X-Y, box:CATEGORY, category:X, option:X. Append =Label for custom display names (e.g., range:4-5=Agree)</t>
   </si>
   <si>
     <t xml:space="preserve">Q01_Awareness</t>
@@ -554,10 +728,37 @@
     <t xml:space="preserve">auto</t>
   </si>
   <si>
+    <t xml:space="preserve">Q06_Agreement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Agreement (1-5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% Agree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean,box:Agree=Top Box,bottom_box</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q07_CX_Index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Experience Index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Composite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CX Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summary Indices</t>
+  </si>
+  <si>
     <t xml:space="preserve">TURAS Tracker - Banner Definitions</t>
   </si>
   <si>
-    <t xml:space="preserve">Define banner break variables for subgroup analysis. Column names can differ across waves.</t>
+    <t xml:space="preserve">Define banner break variables for subgroup analysis. Column names can differ across waves. Add more wave columns (W5, W6, ...) as needed.</t>
   </si>
   <si>
     <t xml:space="preserve">BreakVariable</t>
@@ -566,7 +767,10 @@
     <t xml:space="preserve">BreakLabel</t>
   </si>
   <si>
-    <t xml:space="preserve">[REQUIRED] Variable name used as the banner break (e.g., Total, Region)</t>
+    <t xml:space="preserve">W4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[REQUIRED] Canonical variable name for this banner break (e.g., Total, Region)</t>
   </si>
   <si>
     <t xml:space="preserve">[REQUIRED] Display label for this banner break in report headers</t>
@@ -581,6 +785,9 @@
     <t xml:space="preserve">[Optional] Column name in Wave 3 data for this break variable</t>
   </si>
   <si>
+    <t xml:space="preserve">[Optional] Column name in Wave 4 data for this break variable</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total</t>
   </si>
   <si>
@@ -606,6 +813,15 @@
   </si>
   <si>
     <t xml:space="preserve">DEM_Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q_Gender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEM_Gender</t>
   </si>
 </sst>
 </file>
@@ -1290,37 +1506,37 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
+      <c r="B14" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="E15" s="14" t="s">
+      <c r="A15" s="9" t="s">
         <v>39</v>
       </c>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
     </row>
     <row r="16">
       <c r="A16" s="15" t="s">
         <v>40</v>
       </c>
       <c r="B16" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>4</v>
@@ -1329,32 +1545,32 @@
         <v>41</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="14" t="s">
         <v>42</v>
-      </c>
-      <c r="B17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="B18" s="11" t="s">
         <v>45</v>
+      </c>
+      <c r="B18" s="11" t="n">
+        <v>0</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>4</v>
@@ -1363,58 +1579,58 @@
         <v>46</v>
       </c>
       <c r="E18" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="s">
+      <c r="B19" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
+      <c r="C19" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="B20" s="11" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="E20" s="14" t="s">
+      <c r="A20" s="9" t="s">
         <v>51</v>
       </c>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
     </row>
     <row r="21">
       <c r="A21" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="13" t="s">
+      <c r="E21" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="E21" s="14" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="11" t="s">
         <v>56</v>
-      </c>
-      <c r="B22" s="11" t="n">
-        <v>30</v>
       </c>
       <c r="C22" s="16" t="s">
         <v>4</v>
@@ -1430,17 +1646,17 @@
       <c r="A23" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="13" t="s">
+      <c r="E23" s="14" t="s">
         <v>61</v>
-      </c>
-      <c r="E23" s="14" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="24">
@@ -1448,47 +1664,55 @@
         <v>62</v>
       </c>
       <c r="B24" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
+      <c r="C25" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="C26" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
@@ -1497,10 +1721,10 @@
     </row>
     <row r="28">
       <c r="A28" s="15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>4</v>
@@ -1513,54 +1737,46 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="B29" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="E29" s="14" t="s">
-        <v>77</v>
-      </c>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
     </row>
     <row r="30">
       <c r="A30" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="E30" s="14" t="s">
         <v>78</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="B31" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D31" s="13" t="s">
+      <c r="E31" s="14" t="s">
         <v>82</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="32">
@@ -1594,7 +1810,7 @@
         <v>87</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34">
@@ -1628,21 +1844,29 @@
         <v>92</v>
       </c>
       <c r="E35" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="s">
+      <c r="B36" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
+      <c r="E36" s="14" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>14</v>
@@ -1651,46 +1875,387 @@
         <v>4</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="B38" s="11" t="s">
+      <c r="A38" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B39" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C38" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D38" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="E38" s="14" t="s">
-        <v>80</v>
+      <c r="C39" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="B45" s="11" t="n">
+        <v>70</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="B46" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="E46" s="14" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E49" s="14" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="E50" s="14" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="B51" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="C51" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="E51" s="14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="B52" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="E52" s="14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="B53" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="C53" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="E53" s="14" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="B54" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="E54" s="14" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="B55" s="9"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="C56" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="E56" s="14" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="E58" s="14" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C59" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="E59" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C60" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="E60" s="14" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="12">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A6:E6"/>
     <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A20:E20"/>
     <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A57:E57"/>
   </mergeCells>
-  <dataValidations count="5">
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B15:B15">
-      <formula1>0</formula1>
-      <formula2>3</formula2>
-    </dataValidation>
+  <dataValidations count="11">
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16:B16">
       <formula1>0</formula1>
       <formula2>3</formula2>
@@ -1699,20 +2264,48 @@
       <formula1>0</formula1>
       <formula2>3</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20:B20">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B18:B18">
+      <formula1>0</formula1>
+      <formula2>3</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B21:B21">
       <formula1>0.01</formula1>
       <formula2>0.1</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B22:B22">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B23:B23">
       <formula1>10</formula1>
       <formula2>500</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B45:B45">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B46:B46">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B51:B51">
+      <formula1>-100</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B52:B52">
+      <formula1>-100</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B53:B53">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B54:B54">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"detailed,wave_history,dashboard,sig_matrix,tracking_crosstab,detailed,wave_history,detailed,dashboard,detailed,wave_history,dashboard,sig_matrix,detailed,wave_history,dashboard,sig_matrix,tracking_crosstab"</xm:f>
@@ -1729,19 +2322,31 @@
           <x14:formula1>
             <xm:f>".,,"</xm:f>
           </x14:formula1>
-          <xm:sqref>B18:B18</xm:sqref>
+          <xm:sqref>B19:B19</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"0.90,0.95,0.99"</xm:f>
           </x14:formula1>
-          <xm:sqref>B21:B21</xm:sqref>
+          <xm:sqref>B22:B22</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"Y,N"</xm:f>
           </x14:formula1>
-          <xm:sqref>B23:B23</xm:sqref>
+          <xm:sqref>B24:B24</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"Y,N"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B26:B26</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"default,muted,vibrant,monochrome"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B56:B56</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1766,84 +2371,84 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>101</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>102</v>
+        <v>160</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>103</v>
+        <v>161</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>104</v>
+        <v>162</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>105</v>
+        <v>163</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>106</v>
+        <v>164</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>107</v>
+        <v>165</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>108</v>
+        <v>166</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>109</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>110</v>
+        <v>168</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>111</v>
+        <v>169</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>113</v>
+        <v>171</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>114</v>
+        <v>172</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>116</v>
+        <v>174</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>117</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>118</v>
+        <v>176</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>119</v>
+        <v>177</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>120</v>
+        <v>178</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>121</v>
+        <v>179</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>122</v>
+        <v>180</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>123</v>
+        <v>181</v>
       </c>
       <c r="G5" s="17" t="s">
         <v>14</v>
@@ -1854,22 +2459,22 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>124</v>
+        <v>182</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>125</v>
+        <v>183</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>126</v>
+        <v>184</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>127</v>
+        <v>185</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>128</v>
+        <v>186</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>123</v>
+        <v>181</v>
       </c>
       <c r="G6" s="17" t="s">
         <v>14</v>
@@ -1880,22 +2485,22 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>129</v>
+        <v>187</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>130</v>
+        <v>188</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>131</v>
+        <v>189</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>132</v>
+        <v>190</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>133</v>
+        <v>191</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>123</v>
+        <v>181</v>
       </c>
       <c r="G7" s="17" t="s">
         <v>14</v>
@@ -2130,192 +2735,220 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>134</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>135</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>136</v>
+        <v>194</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>138</v>
+        <v>196</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>139</v>
+        <v>197</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>140</v>
+        <v>198</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>141</v>
+        <v>199</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>142</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>143</v>
+        <v>201</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>144</v>
+        <v>202</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>145</v>
+        <v>203</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>146</v>
+        <v>204</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>147</v>
+        <v>205</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>148</v>
+        <v>206</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>149</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>150</v>
+        <v>208</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>151</v>
+        <v>209</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>152</v>
+        <v>210</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>153</v>
+        <v>211</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>154</v>
+        <v>212</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>155</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>156</v>
+        <v>214</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>157</v>
+        <v>215</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>158</v>
+        <v>216</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>159</v>
+        <v>217</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>160</v>
+        <v>218</v>
       </c>
       <c r="F6" s="17" t="n">
         <v>2</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>161</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>162</v>
+        <v>220</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>163</v>
+        <v>221</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>164</v>
+        <v>222</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>165</v>
+        <v>223</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>166</v>
+        <v>224</v>
       </c>
       <c r="F7" s="17" t="n">
         <v>3</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>167</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>168</v>
+        <v>226</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>169</v>
+        <v>227</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>152</v>
+        <v>210</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>170</v>
+        <v>228</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>171</v>
+        <v>229</v>
       </c>
       <c r="F8" s="17" t="n">
         <v>4</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>172</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="s">
-        <v>173</v>
+        <v>231</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>174</v>
+        <v>232</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>175</v>
+        <v>233</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>176</v>
+        <v>234</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>177</v>
+        <v>235</v>
       </c>
       <c r="F9" s="17" t="n">
         <v>5</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>178</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
+      <c r="A10" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
+      <c r="A11" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>242</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>244</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>245</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="11"/>
@@ -2749,13 +3382,31 @@
       <c r="F59" s="11"/>
       <c r="G59" s="11"/>
     </row>
+    <row r="60">
+      <c r="A60" s="11"/>
+      <c r="B60" s="11"/>
+      <c r="C60" s="11"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="11"/>
+      <c r="B61" s="11"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F59">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F61">
       <formula1>1</formula1>
       <formula2>999</formula2>
     </dataValidation>
@@ -2769,7 +3420,7 @@
           <x14:formula1>
             <xm:f>"Rating,NPS,Single_Response,Multi_Mention,Composite"</xm:f>
           </x14:formula1>
-          <xm:sqref>C5:C59</xm:sqref>
+          <xm:sqref>C5:C61</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2787,109 +3438,138 @@
     <col min="3" max="3" width="18.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="18.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="18.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="18.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>179</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>181</v>
+        <v>248</v>
       </c>
       <c r="B3" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>124</v>
-      </c>
       <c r="E3" s="8" t="s">
-        <v>129</v>
+        <v>187</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>183</v>
+        <v>251</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>184</v>
+        <v>252</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>185</v>
+        <v>253</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>186</v>
+        <v>254</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>187</v>
+        <v>255</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>188</v>
+        <v>257</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>189</v>
+        <v>258</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>188</v>
+        <v>257</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>188</v>
+        <v>257</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>188</v>
+        <v>257</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>190</v>
+        <v>259</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>190</v>
+        <v>259</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>191</v>
+        <v>260</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>191</v>
+        <v>260</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>192</v>
+        <v>261</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>193</v>
+        <v>262</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>194</v>
+        <v>263</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>195</v>
+        <v>264</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>195</v>
+        <v>264</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>196</v>
+        <v>265</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
+      <c r="A8" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>267</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>267</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11"/>
@@ -2897,6 +3577,7 @@
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
     </row>
     <row r="10">
       <c r="A10" s="11"/>
@@ -2904,6 +3585,7 @@
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
     </row>
     <row r="11">
       <c r="A11" s="11"/>
@@ -2911,6 +3593,7 @@
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
     </row>
     <row r="12">
       <c r="A12" s="11"/>
@@ -2918,6 +3601,7 @@
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
     </row>
     <row r="13">
       <c r="A13" s="11"/>
@@ -2925,6 +3609,7 @@
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
     </row>
     <row r="14">
       <c r="A14" s="11"/>
@@ -2932,6 +3617,7 @@
       <c r="C14" s="11"/>
       <c r="D14" s="11"/>
       <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
     </row>
     <row r="15">
       <c r="A15" s="11"/>
@@ -2939,6 +3625,7 @@
       <c r="C15" s="11"/>
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
     </row>
     <row r="16">
       <c r="A16" s="11"/>
@@ -2946,6 +3633,7 @@
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
     </row>
     <row r="17">
       <c r="A17" s="11"/>
@@ -2953,6 +3641,7 @@
       <c r="C17" s="11"/>
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
     </row>
     <row r="18">
       <c r="A18" s="11"/>
@@ -2960,6 +3649,7 @@
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
     </row>
     <row r="19">
       <c r="A19" s="11"/>
@@ -2967,6 +3657,7 @@
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
     </row>
     <row r="20">
       <c r="A20" s="11"/>
@@ -2974,6 +3665,7 @@
       <c r="C20" s="11"/>
       <c r="D20" s="11"/>
       <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
     </row>
     <row r="21">
       <c r="A21" s="11"/>
@@ -2981,6 +3673,7 @@
       <c r="C21" s="11"/>
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
     </row>
     <row r="22">
       <c r="A22" s="11"/>
@@ -2988,6 +3681,7 @@
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
     </row>
     <row r="23">
       <c r="A23" s="11"/>
@@ -2995,6 +3689,7 @@
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
       <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
     </row>
     <row r="24">
       <c r="A24" s="11"/>
@@ -3002,6 +3697,7 @@
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
       <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
     </row>
     <row r="25">
       <c r="A25" s="11"/>
@@ -3009,6 +3705,7 @@
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
       <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
     </row>
     <row r="26">
       <c r="A26" s="11"/>
@@ -3016,6 +3713,7 @@
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
       <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
     </row>
     <row r="27">
       <c r="A27" s="11"/>
@@ -3023,11 +3721,20 @@
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
       <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/modules/tracker/docs/templates/Tracking_Config.xlsx
+++ b/modules/tracker/docs/templates/Tracking_Config.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="278">
   <si>
     <t xml:space="preserve">TURAS Tracker - Configuration Settings</t>
   </si>
@@ -489,6 +489,33 @@
   </si>
   <si>
     <t xml:space="preserve">JSON array string or leave blank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate_Stats_Pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generate a diagnostic stats pack workbook alongside main output. The stats pack provides a full audit trail of data received, methods used, assumptions, and reproducibility — designed for advanced partners and research statisticians. Output file is named {output}_stats_pack.xlsx.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STUDY IDENTIFICATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project name — appears in the stats pack Declaration sheet for identification and sign-off purposes. Leave blank if not using stats pack.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analyst_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analyst name — appears in the stats pack Declaration sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research_House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research organisation name — appears in the stats pack Declaration sheet. Use your company or white-label partner name.</t>
   </si>
   <si>
     <t xml:space="preserve">TURAS Tracker - Wave Definitions</t>
@@ -2240,8 +2267,85 @@
         <v>157</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="E61" s="14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B62" s="9"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="9"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C63" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D63" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="E63" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D64" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="E64" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C65" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D65" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="E65" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A6:E6"/>
@@ -2254,6 +2358,7 @@
     <mergeCell ref="A44:E44"/>
     <mergeCell ref="A55:E55"/>
     <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A62:E62"/>
   </mergeCells>
   <dataValidations count="11">
     <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16:B16">
@@ -2305,7 +2410,7 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="8">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>"detailed,wave_history,dashboard,sig_matrix,tracking_crosstab,detailed,wave_history,detailed,dashboard,detailed,wave_history,dashboard,sig_matrix,detailed,wave_history,dashboard,sig_matrix,tracking_crosstab"</xm:f>
@@ -2348,6 +2453,12 @@
           </x14:formula1>
           <xm:sqref>B56:B56</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>"Y,N"</xm:f>
+          </x14:formula1>
+          <xm:sqref>B61:B61</xm:sqref>
+        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -2371,84 +2482,84 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="G5" s="17" t="s">
         <v>14</v>
@@ -2459,22 +2570,22 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="G6" s="17" t="s">
         <v>14</v>
@@ -2485,22 +2596,22 @@
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="D7" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="F7" s="17" t="s">
         <v>190</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>181</v>
       </c>
       <c r="G7" s="17" t="s">
         <v>14</v>
@@ -2735,219 +2846,219 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="F6" s="17" t="n">
         <v>2</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F7" s="17" t="n">
         <v>3</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="F8" s="17" t="n">
         <v>4</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="17" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="F9" s="17" t="n">
         <v>5</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="F10" s="17" t="n">
         <v>6</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="17" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F11" s="17" t="n">
         <v>7</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12">
@@ -3443,132 +3554,132 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="17" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="17" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9">
